--- a/data/trans_dic/P6901-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,53; 86,87</t>
+          <t>58,55; 86,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,27; 82,27</t>
+          <t>52,14; 83,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,6; 72,14</t>
+          <t>45,02; 71,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,46; 82,47</t>
+          <t>42,81; 82,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,37; 88,47</t>
+          <t>53,22; 88,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,99; 90,64</t>
+          <t>58,06; 92,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,0; 82,38</t>
+          <t>54,04; 82,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,34; 87,98</t>
+          <t>47,53; 89,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,13; 82,25</t>
+          <t>60,49; 83,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,8; 82,44</t>
+          <t>61,65; 82,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,82; 73,72</t>
+          <t>52,82; 72,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,09; 80,77</t>
+          <t>50,99; 82,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,58; 89,87</t>
+          <t>69,92; 90,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,52; 95,05</t>
+          <t>78,94; 96,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,47; 96,19</t>
+          <t>83,1; 96,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,86; 92,62</t>
+          <t>66,82; 93,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,93; 96,93</t>
+          <t>71,17; 96,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,8; 91,06</t>
+          <t>62,33; 91,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,71; 97,46</t>
+          <t>76,83; 97,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,6; 96,27</t>
+          <t>77,31; 95,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,2; 90,01</t>
+          <t>75,1; 90,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76,73; 92,19</t>
+          <t>76,89; 91,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,27; 95,04</t>
+          <t>83,7; 94,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,48; 92,29</t>
+          <t>76,11; 92,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,16; 89,73</t>
+          <t>64,17; 89,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,18; 96,41</t>
+          <t>70,49; 96,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,32; 95,73</t>
+          <t>61,44; 95,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,48; 69,11</t>
+          <t>42,88; 70,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,54; 86,84</t>
+          <t>50,34; 86,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,6; 94,41</t>
+          <t>53,11; 94,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,91; 100,0</t>
+          <t>54,34; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,55; 79,98</t>
+          <t>58,42; 80,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,92; 85,35</t>
+          <t>62,66; 85,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70,73; 93,44</t>
+          <t>70,61; 93,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,81; 92,87</t>
+          <t>66,83; 92,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,38; 71,59</t>
+          <t>54,23; 71,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,62; 83,86</t>
+          <t>59,38; 83,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 93,01</t>
+          <t>72,77; 94,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,99; 92,88</t>
+          <t>63,64; 91,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,68; 84,54</t>
+          <t>49,21; 85,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,48; 88,37</t>
+          <t>51,38; 88,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,88; 89,89</t>
+          <t>56,82; 90,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,14; 93,86</t>
+          <t>69,74; 93,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,68; 95,58</t>
+          <t>69,83; 95,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,39; 82,46</t>
+          <t>62,27; 82,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,1; 89,07</t>
+          <t>72,3; 89,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,37; 90,49</t>
+          <t>71,37; 90,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,19; 92,81</t>
+          <t>66,37; 90,8</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,33; 87,75</t>
+          <t>47,54; 86,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,13; 93,65</t>
+          <t>49,29; 93,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,82; 100,0</t>
+          <t>54,56; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,2; 95,89</t>
+          <t>68,03; 95,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,17; 100,0</t>
+          <t>27,96; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,13; 100,0</t>
+          <t>50,65; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,12; 100,0</t>
+          <t>35,48; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,85; 96,0</t>
+          <t>64,36; 96,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,93; 83,91</t>
+          <t>48,24; 84,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,97; 90,75</t>
+          <t>61,11; 92,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55,92; 95,54</t>
+          <t>59,63; 95,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,39; 92,8</t>
+          <t>73,25; 92,31</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,21; 87,83</t>
+          <t>60,6; 87,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,26; 87,66</t>
+          <t>60,18; 86,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,38; 69,39</t>
+          <t>25,87; 68,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,99; 81,71</t>
+          <t>50,35; 80,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,33; 92,66</t>
+          <t>45,78; 92,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,19; 100,0</t>
+          <t>66,07; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,66; 86,03</t>
+          <t>59,63; 85,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,45; 85,84</t>
+          <t>64,25; 85,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65,3; 88,19</t>
+          <t>66,7; 87,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42,35; 80,06</t>
+          <t>43,58; 78,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60,75; 80,75</t>
+          <t>60,69; 80,58</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,92; 76,51</t>
+          <t>56,94; 76,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,51; 63,33</t>
+          <t>35,45; 62,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,52; 90,59</t>
+          <t>70,79; 90,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,43; 78,89</t>
+          <t>54,75; 77,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,74; 92,95</t>
+          <t>71,16; 93,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,78; 82,68</t>
+          <t>55,09; 84,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,27; 97,0</t>
+          <t>78,69; 96,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,11; 83,43</t>
+          <t>62,25; 82,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,9; 80,66</t>
+          <t>64,75; 80,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,4; 68,97</t>
+          <t>48,69; 67,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78,21; 91,24</t>
+          <t>77,95; 92,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,32; 77,88</t>
+          <t>62,49; 78,44</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>69,8; 85,14</t>
+          <t>70,09; 85,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56,38; 82,86</t>
+          <t>56,39; 84,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,65; 65,65</t>
+          <t>31,74; 64,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,59; 96,59</t>
+          <t>82,03; 96,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,93; 85,78</t>
+          <t>60,78; 85,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,75; 96,32</t>
+          <t>64,14; 96,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,92; 95,32</t>
+          <t>59,08; 95,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,64; 85,91</t>
+          <t>48,36; 85,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,29; 83,55</t>
+          <t>70,95; 83,84</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64,08; 85,21</t>
+          <t>65,53; 86,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47,39; 72,75</t>
+          <t>46,97; 72,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,93; 89,38</t>
+          <t>68,45; 89,77</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70,83; 78,8</t>
+          <t>71,04; 78,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,29; 79,44</t>
+          <t>69,39; 79,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,64; 79,32</t>
+          <t>69,38; 78,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67,51; 77,89</t>
+          <t>67,47; 77,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,08</t>
+          <t>71,9; 83,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,79; 83,76</t>
+          <t>71,63; 83,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,06; 88,9</t>
+          <t>79,65; 89,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>72,4; 84,1</t>
+          <t>72,53; 84,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72,42; 79,35</t>
+          <t>72,43; 78,97</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,98; 79,67</t>
+          <t>71,76; 79,34</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74,75; 82,01</t>
+          <t>74,66; 81,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>71,84; 79,81</t>
+          <t>71,71; 79,64</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25077; 37220</t>
+          <t>25087; 37054</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20249; 32492</t>
+          <t>20592; 32905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26128; 42259</t>
+          <t>26374; 41913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9979; 19851</t>
+          <t>10303; 19937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14988; 25318</t>
+          <t>15231; 25361</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16784; 25360</t>
+          <t>16243; 25893</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21261; 33682</t>
+          <t>22094; 33686</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7300; 13862</t>
+          <t>7489; 14022</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42972; 58776</t>
+          <t>43229; 59344</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40346; 55624</t>
+          <t>41596; 55968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52533; 73318</t>
+          <t>52537; 72526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20346; 32167</t>
+          <t>20305; 32900</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50376; 65061</t>
+          <t>50622; 65203</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43867; 53791</t>
+          <t>44674; 54591</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69099; 79630</t>
+          <t>68798; 79678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30479; 42866</t>
+          <t>30927; 43067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23838; 31685</t>
+          <t>23266; 31690</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21207; 31249</t>
+          <t>21390; 31285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33182; 41612</t>
+          <t>32804; 41534</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35719; 43749</t>
+          <t>35130; 43372</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77975; 94586</t>
+          <t>78918; 94677</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69752; 83804</t>
+          <t>69894; 83504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>105750; 119259</t>
+          <t>105023; 118947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70147; 84654</t>
+          <t>69807; 84415</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22760; 32856</t>
+          <t>23496; 32743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18772; 24396</t>
+          <t>17837; 24393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12820; 20346</t>
+          <t>13059; 20355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21026; 34206</t>
+          <t>21223; 34784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10111; 18866</t>
+          <t>10936; 18867</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9613; 16933</t>
+          <t>9525; 16930</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7239; 12501</t>
+          <t>6793; 12501</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26432; 36730</t>
+          <t>26829; 36888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36710; 49792</t>
+          <t>36556; 49839</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30584; 40403</t>
+          <t>30532; 40336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23565; 31347</t>
+          <t>22559; 31227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51891; 68308</t>
+          <t>51749; 68518</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35353; 48909</t>
+          <t>34632; 48543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33658; 43778</t>
+          <t>34253; 44305</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21425; 30154</t>
+          <t>20660; 29768</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19239; 34115</t>
+          <t>19857; 34527</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12143; 20066</t>
+          <t>11665; 20133</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16800; 26548</t>
+          <t>16782; 26620</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20098; 28098</t>
+          <t>20876; 28108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55395; 77091</t>
+          <t>56315; 77369</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50551; 66817</t>
+          <t>50459; 66457</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55228; 68231</t>
+          <t>55382; 68494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44536; 56463</t>
+          <t>44533; 56588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81301; 112301</t>
+          <t>80305; 109873</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11094; 20141</t>
+          <t>10913; 19920</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8106; 15141</t>
+          <t>7970; 15148</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7705; 14870</t>
+          <t>8113; 14870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11933; 17026</t>
+          <t>12081; 17037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1963; 6970</t>
+          <t>1948; 6970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5845; 11661</t>
+          <t>5907; 11661</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2027; 5771</t>
+          <t>2047; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7124; 10546</t>
+          <t>7071; 10605</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15541; 25110</t>
+          <t>14437; 25359</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16410; 25256</t>
+          <t>17006; 25687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11543; 19721</t>
+          <t>12307; 19754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20806; 26673</t>
+          <t>21054; 26534</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25594; 36720</t>
+          <t>25335; 36757</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25708; 38028</t>
+          <t>26105; 37340</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6367; 15567</t>
+          <t>5803; 15466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16436; 25834</t>
+          <t>15918; 25529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5825; 13059</t>
+          <t>6452; 13055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10050; 15184</t>
+          <t>10032; 15184</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5700; 7427</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18027; 25992</t>
+          <t>18018; 25873</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34909; 47984</t>
+          <t>35916; 47876</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38244; 51646</t>
+          <t>39064; 51403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12647; 23906</t>
+          <t>13014; 23442</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37561; 49930</t>
+          <t>37527; 49825</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49456; 67672</t>
+          <t>50361; 68020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18785; 34471</t>
+          <t>19296; 34052</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56034; 70971</t>
+          <t>55462; 70637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40564; 57728</t>
+          <t>40068; 56690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31667; 40468</t>
+          <t>30979; 40750</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24942; 38348</t>
+          <t>25549; 38996</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43026; 54011</t>
+          <t>43818; 54002</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44510; 58837</t>
+          <t>43904; 58180</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>85660; 106459</t>
+          <t>85455; 105920</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48792; 69532</t>
+          <t>49081; 68403</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104822; 122279</t>
+          <t>104467; 123425</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>90999; 111913</t>
+          <t>89795; 112716</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76024; 92733</t>
+          <t>76337; 93230</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25437; 37384</t>
+          <t>25442; 38017</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12429; 25782</t>
+          <t>12465; 25257</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45741; 54821</t>
+          <t>46559; 54822</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30832; 42705</t>
+          <t>30262; 42609</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19554; 29542</t>
+          <t>19672; 29616</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12395; 20399</t>
+          <t>12643; 20396</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27705; 47003</t>
+          <t>26455; 46731</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113145; 132588</t>
+          <t>112595; 133053</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48566; 64582</t>
+          <t>49663; 65261</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28755; 44141</t>
+          <t>28497; 44145</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>76834; 99634</t>
+          <t>76297; 100060</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>334550; 372165</t>
+          <t>335509; 372213</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>226963; 260196</t>
+          <t>227282; 259495</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>243733; 277615</t>
+          <t>242826; 274945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>229201; 264426</t>
+          <t>229067; 262543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>158216; 182869</t>
+          <t>158264; 183829</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>153383; 178952</t>
+          <t>153048; 177544</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>171011; 192299</t>
+          <t>172284; 193490</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>256445; 297888</t>
+          <t>256929; 297664</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>501482; 549421</t>
+          <t>501537; 546815</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>389548; 431185</t>
+          <t>388400; 429377</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>423295; 464402</t>
+          <t>422810; 463700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>498342; 553674</t>
+          <t>497433; 552447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6901-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,55; 86,49</t>
+          <t>59,3; 86,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,14; 83,32</t>
+          <t>51,33; 83,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,02; 71,55</t>
+          <t>44,37; 72,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,81; 82,83</t>
+          <t>49,21; 83,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,22; 88,61</t>
+          <t>50,11; 86,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,06; 92,55</t>
+          <t>56,75; 89,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 82,39</t>
+          <t>54,23; 83,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,53; 89,0</t>
+          <t>50,27; 86,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,49; 83,04</t>
+          <t>61,37; 83,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,65; 82,95</t>
+          <t>58,6; 82,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,82; 72,92</t>
+          <t>52,94; 72,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,99; 82,61</t>
+          <t>55,16; 81,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,92; 90,06</t>
+          <t>70,22; 89,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,94; 96,47</t>
+          <t>78,27; 95,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,1; 96,25</t>
+          <t>81,51; 96,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,82; 93,06</t>
+          <t>69,19; 94,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,17; 96,95</t>
+          <t>72,48; 96,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,33; 91,17</t>
+          <t>62,63; 91,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,83; 97,28</t>
+          <t>76,86; 97,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,31; 95,44</t>
+          <t>78,12; 95,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75,1; 90,1</t>
+          <t>75,15; 90,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76,89; 91,86</t>
+          <t>76,48; 91,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,7; 94,79</t>
+          <t>83,95; 95,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,11; 92,03</t>
+          <t>76,71; 92,03</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,17; 89,42</t>
+          <t>63,53; 89,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,49; 96,39</t>
+          <t>73,72; 96,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,44; 95,77</t>
+          <t>62,34; 95,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,88; 70,28</t>
+          <t>42,76; 69,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,34; 86,85</t>
+          <t>46,47; 86,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,11; 94,4</t>
+          <t>52,81; 94,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,34; 100,0</t>
+          <t>60,67; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,42; 80,32</t>
+          <t>56,26; 78,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,66; 85,43</t>
+          <t>62,94; 85,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70,61; 93,28</t>
+          <t>69,8; 93,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,83; 92,51</t>
+          <t>66,54; 92,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,23; 71,81</t>
+          <t>53,48; 71,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,38; 83,23</t>
+          <t>59,84; 83,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,77; 94,13</t>
+          <t>71,08; 93,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,64; 91,69</t>
+          <t>63,89; 93,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,21; 85,56</t>
+          <t>51,25; 85,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,38; 88,67</t>
+          <t>55,61; 91,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,82; 90,13</t>
+          <t>56,49; 90,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,74; 93,9</t>
+          <t>66,92; 93,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,83; 95,93</t>
+          <t>62,56; 84,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,27; 82,02</t>
+          <t>63,08; 82,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,3; 89,41</t>
+          <t>71,71; 89,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,37; 90,69</t>
+          <t>71,47; 90,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,37; 90,8</t>
+          <t>62,44; 82,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,54; 86,78</t>
+          <t>46,09; 87,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,29; 93,69</t>
+          <t>49,54; 93,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,56; 100,0</t>
+          <t>55,11; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68,03; 95,95</t>
+          <t>68,21; 96,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,96; 100,0</t>
+          <t>28,17; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,65; 100,0</t>
+          <t>53,0; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,48; 100,0</t>
+          <t>34,38; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,36; 96,53</t>
+          <t>64,17; 96,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,24; 84,74</t>
+          <t>51,56; 84,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,11; 92,3</t>
+          <t>58,01; 90,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,63; 95,7</t>
+          <t>60,88; 95,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,25; 92,31</t>
+          <t>74,28; 94,15</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60,6; 87,91</t>
+          <t>60,97; 87,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,18; 86,08</t>
+          <t>60,34; 86,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,87; 68,94</t>
+          <t>29,01; 69,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,35; 80,75</t>
+          <t>53,4; 82,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,78; 92,63</t>
+          <t>45,81; 92,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,07; 100,0</t>
+          <t>65,64; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,63; 85,63</t>
+          <t>60,1; 86,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64,25; 85,64</t>
+          <t>62,76; 85,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,7; 87,77</t>
+          <t>66,05; 87,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,58; 78,51</t>
+          <t>41,91; 77,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>60,69; 80,58</t>
+          <t>62,79; 81,18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,94; 76,9</t>
+          <t>56,75; 77,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,45; 62,56</t>
+          <t>34,62; 62,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,79; 90,17</t>
+          <t>72,01; 90,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54,75; 77,47</t>
+          <t>58,35; 80,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,16; 93,6</t>
+          <t>72,7; 93,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,09; 84,08</t>
+          <t>54,18; 82,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,69; 96,98</t>
+          <t>77,96; 96,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,25; 82,49</t>
+          <t>66,99; 84,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,75; 80,25</t>
+          <t>64,83; 80,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,69; 67,85</t>
+          <t>47,71; 68,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77,95; 92,09</t>
+          <t>78,08; 91,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,49; 78,44</t>
+          <t>65,72; 79,59</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,09; 85,6</t>
+          <t>70,53; 85,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56,39; 84,26</t>
+          <t>56,28; 83,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,74; 64,31</t>
+          <t>30,58; 63,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,03; 96,59</t>
+          <t>82,64; 96,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,78; 85,58</t>
+          <t>61,54; 85,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,14; 96,56</t>
+          <t>64,36; 96,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,08; 95,31</t>
+          <t>57,19; 95,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,36; 85,42</t>
+          <t>70,07; 90,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,95; 83,84</t>
+          <t>70,84; 83,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65,53; 86,11</t>
+          <t>64,46; 85,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,97; 72,76</t>
+          <t>47,57; 72,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,45; 89,77</t>
+          <t>80,13; 92,07</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,81</t>
+          <t>70,82; 79,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,39; 79,22</t>
+          <t>69,03; 78,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69,38; 78,56</t>
+          <t>69,24; 79,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67,47; 77,33</t>
+          <t>69,95; 79,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,9; 83,51</t>
+          <t>72,29; 83,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,63; 83,1</t>
+          <t>70,59; 83,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,65; 89,46</t>
+          <t>79,3; 89,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>72,53; 84,03</t>
+          <t>73,44; 81,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72,43; 78,97</t>
+          <t>72,44; 79,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,76; 79,34</t>
+          <t>71,93; 79,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74,66; 81,88</t>
+          <t>75,14; 82,04</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>71,71; 79,64</t>
+          <t>72,95; 79,26</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26811</t>
+          <t>29849</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25087; 37054</t>
+          <t>25407; 37116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20592; 32905</t>
+          <t>20271; 32943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26374; 41913</t>
+          <t>25989; 42365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10303; 19937</t>
+          <t>12898; 21997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15231; 25361</t>
+          <t>14340; 24763</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16243; 25893</t>
+          <t>15878; 25071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22094; 33686</t>
+          <t>22170; 33983</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7489; 14022</t>
+          <t>8146; 13951</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43229; 59344</t>
+          <t>43858; 59485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41596; 55968</t>
+          <t>39536; 55583</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52537; 72526</t>
+          <t>52652; 72235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20305; 32900</t>
+          <t>23400; 34582</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38359</t>
+          <t>40187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78617</t>
+          <t>81165</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50622; 65203</t>
+          <t>50834; 65040</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44674; 54591</t>
+          <t>44292; 53876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68798; 79678</t>
+          <t>67483; 79601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30927; 43067</t>
+          <t>33215; 45298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23266; 31690</t>
+          <t>23691; 31698</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21390; 31285</t>
+          <t>21490; 31384</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32804; 41534</t>
+          <t>32817; 41515</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35130; 43372</t>
+          <t>36331; 44189</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78918; 94677</t>
+          <t>78970; 94838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69894; 83504</t>
+          <t>69520; 83385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>105023; 118947</t>
+          <t>105343; 119205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69807; 84415</t>
+          <t>72496; 86984</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>60582</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23496; 32743</t>
+          <t>23263; 32830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17837; 24393</t>
+          <t>18656; 24388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13059; 20355</t>
+          <t>13251; 20336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21223; 34784</t>
+          <t>21207; 34342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10936; 18867</t>
+          <t>10096; 18799</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9525; 16930</t>
+          <t>9472; 16919</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6793; 12501</t>
+          <t>7584; 12501</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26829; 36888</t>
+          <t>26421; 36864</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36556; 49839</t>
+          <t>36719; 49646</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30532; 40336</t>
+          <t>30182; 40253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22559; 31227</t>
+          <t>22459; 31144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51749; 68518</t>
+          <t>51641; 68783</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68024</t>
+          <t>39756</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95622</t>
+          <t>78541</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34632; 48543</t>
+          <t>34902; 48466</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34253; 44305</t>
+          <t>33457; 44040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20660; 29768</t>
+          <t>20741; 30285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19857; 34527</t>
+          <t>27762; 46408</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11665; 20133</t>
+          <t>12626; 20725</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16782; 26620</t>
+          <t>16683; 26604</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20876; 28108</t>
+          <t>20032; 28081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56315; 77369</t>
+          <t>33338; 44881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50459; 66457</t>
+          <t>51113; 66928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55382; 68494</t>
+          <t>54928; 68392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44533; 56588</t>
+          <t>44600; 56712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80305; 109873</t>
+          <t>67094; 88222</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>30094</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10913; 19920</t>
+          <t>10580; 19974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7970; 15148</t>
+          <t>8010; 15145</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8113; 14870</t>
+          <t>8194; 14870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12081; 17037</t>
+          <t>14770; 20903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1948; 6970</t>
+          <t>1963; 6970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5907; 11661</t>
+          <t>6181; 11661</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2047; 5771</t>
+          <t>1984; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7071; 10605</t>
+          <t>8722; 13127</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14437; 25359</t>
+          <t>15429; 25191</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17006; 25687</t>
+          <t>16145; 25157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12307; 19754</t>
+          <t>12567; 19744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21054; 26534</t>
+          <t>26179; 33184</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43850</t>
+          <t>45629</t>
         </is>
       </c>
     </row>
@@ -3249,32 +3249,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25335; 36757</t>
+          <t>25490; 36527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26105; 37340</t>
+          <t>26175; 37535</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5803; 15466</t>
+          <t>6508; 15570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15918; 25529</t>
+          <t>17552; 27241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6452; 13055</t>
+          <t>6457; 13070</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10032; 15184</t>
+          <t>9967; 15184</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18018; 25873</t>
+          <t>18380; 26576</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35916; 47876</t>
+          <t>35087; 47903</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39064; 51403</t>
+          <t>38679; 51426</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13014; 23442</t>
+          <t>12516; 23182</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37527; 49825</t>
+          <t>39839; 51508</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52576</t>
+          <t>61946</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>122103</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50361; 68020</t>
+          <t>50190; 68218</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19296; 34052</t>
+          <t>18845; 34252</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55462; 70637</t>
+          <t>56418; 70909</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40068; 56690</t>
+          <t>50094; 69399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30979; 40750</t>
+          <t>31650; 40699</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25549; 38996</t>
+          <t>25128; 38283</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43818; 54002</t>
+          <t>43408; 53903</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43904; 58180</t>
+          <t>54072; 68273</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>85455; 105920</t>
+          <t>85564; 106390</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49081; 68403</t>
+          <t>48093; 68600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104467; 123425</t>
+          <t>104641; 122980</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89795; 112716</t>
+          <t>109464; 132570</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>108067</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76337; 93230</t>
+          <t>76814; 93406</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25442; 38017</t>
+          <t>25395; 37594</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12465; 25257</t>
+          <t>12009; 24845</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46559; 54822</t>
+          <t>55080; 64492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30262; 42609</t>
+          <t>30638; 42710</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19672; 29616</t>
+          <t>19741; 29594</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12643; 20396</t>
+          <t>12238; 20380</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26455; 46731</t>
+          <t>40279; 52066</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>112595; 133053</t>
+          <t>112428; 133028</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49663; 65261</t>
+          <t>48859; 64686</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28497; 44145</t>
+          <t>28864; 43969</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>76297; 100060</t>
+          <t>99476; 114296</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>246977</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>276261</t>
+          <t>267835</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>523238</t>
+          <t>556030</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>335509; 372213</t>
+          <t>334494; 373635</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>227282; 259495</t>
+          <t>226127; 258741</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>242826; 274945</t>
+          <t>242356; 277379</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>229067; 262543</t>
+          <t>269317; 304522</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>158264; 183829</t>
+          <t>159126; 183386</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>153048; 177544</t>
+          <t>150830; 178059</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>172284; 193490</t>
+          <t>171528; 194382</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>256929; 297664</t>
+          <t>253612; 280893</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>501537; 546815</t>
+          <t>501604; 547366</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>388400; 429377</t>
+          <t>389279; 428998</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>422810; 463700</t>
+          <t>425538; 464599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>497433; 552447</t>
+          <t>532766; 578889</t>
         </is>
       </c>
     </row>
